--- a/risultati/decision_matrix_ACN_membership_DP.xlsx
+++ b/risultati/decision_matrix_ACN_membership_DP.xlsx
@@ -508,14 +508,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
@@ -563,7 +563,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="185" customHeight="1">
+    <row r="2" ht="200" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Popolazione e dati</t>
@@ -576,12 +576,12 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>ACN-Data, 3 siti reali: caltech, jpl, office1. Anni 2018-2021, office1 dal 2019 (il 2018 non esiste su ev.caltech.edu). Sessioni caricate: caltech 31.404, jpl 33.629, office1 1.680. Nessun filtro oltre allo scarto delle sessioni prive delle feature richieste. 6 feature nel regime naturale: total_energy_kwh, max_power_kw, kwh_requested, minutes_available, hour_of_day, duration_hours. Normalizzazione min-max [0,1] calcolata sul training. hour_of_day localizzato al fuso del sito.</t>
+          <t>ACN-Data, 3 siti reali: caltech, jpl, office1. Anni 2018-2021, office1 dal 2019. Sessioni: caltech 31.404, jpl 33.629, office1 1.680 (66.713 totali). Nessun filtro oltre allo scarto delle sessioni prive delle feature richieste. 6 feature nel regime naturale; normalizzazione min-max [0,1] sul training; hour_of_day localizzato al fuso del sito. IDENTIFICATIVI, misurati il 2026-09-21: sessionID 100%, stationID 100%, spaceID 100%, userID 72,6% globale ma molto diseguale fra siti — jpl 93,5%, caltech 52,1%, office1 34,8%.</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Rilevato, non ancora congelato. Identificativi disponibili nel dataset: session_id e user_id; il grado di popolamento di user_id NON e' stato misurato, quindi l'unita' 'persona' non e' ne' esclusa ne' sostenuta dalle evidenze attuali.</t>
+          <t>Rilevato e misurato. Su userID: e' l'unico identificativo che potrebbe sostenere un'unita' 'persona', ed e' anche l'unico non completo. Con office1 al 34,8% un'analisi per persona su quel sito lavorerebbe su un terzo dei dati, con selezione non casuale (chi si registra al servizio). sessionID, stationID e spaceID sono completi ma identificano la sessione o il punto di ricarica, non l'individuo.</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>src/adapters/acn_dataset.py; scripts/run_experiments.py::enrich_sessions, normalize_sessions; config/experiment.yaml (sites:, ml.input_dim, ml.feature_names)</t>
+          <t>scripts/genera_matrici_faseA.py (misura del popolamento); src/adapters/acn_dataset.py; scripts/run_experiments.py::enrich_sessions, normalize_sessions</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>logs/*.log riga 'sessioni caricate' per ogni run; campo config.n_train_sessions nei JSON di experiments/</t>
+          <t>logs/*.log riga 'sessioni caricate'; campo config.n_train_sessions nei JSON; datasets/acn/*/acndata_sessions_*.json per il conteggio degli identificativi</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="185" customHeight="1">
+    <row r="3" ht="200" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Unità di membership</t>
@@ -623,7 +623,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Rilevato e coerente. Il meccanismo DP opera su adiacenza CLIENT-level mentre gli attacchi misurano il RECORD: le due unita' non coincidono. E' un fatto registrato, non un difetto da correggere.</t>
+          <t>Rilevato e coerente. Il meccanismo DP opera su adiacenza CLIENT-level mentre gli attacchi misurano il RECORD: le due unita' non coincidono. E' un fatto registrato, non un difetto da correggere. L'unita' 'persona' resta impraticabile su office1 per il popolamento di userID (vedi riga Popolazione).</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>scripts/run_experiments.py::run_yeom, run_shadow, run_lira (il pool di valutazione e' una lista di sessioni)</t>
+          <t>scripts/run_experiments.py::run_yeom, run_shadow, run_lira</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -647,7 +647,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="185" customHeight="1">
+    <row r="4" ht="200" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Partizioni</t>
@@ -660,279 +660,279 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Split train/holdout 80/20 casuale, previo shuffle con il seed dell'esperimento. cfg['split']['strategy'] esiste con default 'random'; l'alternativa 'entity_aware' non e' impostata in nessun config di campagna. Assegnazione ai client per site_id reale: 3 client = 3 siti. Dati ausiliari dell'attacco: gli shadow di LiRA si addestrano su cluster_members[c] + cluster_holdout[c], cioe' sessioni reali del client; IN/OUT per shadow su meta' dell'universo.</t>
+          <t>Split train/holdout 80/20 casuale previo shuffle con il seed. ASSEGNAZIONE AI CLIENT, dal 2026-09-21 esplicita e registrata: partition.strategy con due valori. 'per_site' (default, storico) = i 3 client SONO i 3 siti, non-IID per natura. 'iid' (nuovo) = sessioni rimescolate FRA i siti conservando esattamente le numerosita' per client, quindi cambia solo la distribuzione delle feature. Dati ausiliari dell'attacco: shadow LiRA su cluster_members[c] + cluster_holdout[c].</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Rilevato. Conseguenza registrata, non risolta: la partizione e' non-IID perche' i client SONO i siti, quindi l'eterogeneita' non e' un fattore manipolato. Nessun riferimento omogeneo esiste fra le 235 run.</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
+          <t>Rilevato E COLMATO come capacita': il braccio IID ora esiste nel codice e nei config (experiment_rq2_iid.yaml contro experiment_rq2_per_site.yaml, identici tranne quel campo). Non e' ancora stato ESEGUITO: la lacuna sperimentale di RQ2 resta aperta e vive in Matrice_sintesi. Da dichiarare nel paper: la partizione IID rompe la corrispondenza client-sito e con essa la coerenza temporale e la separazione fra utenti. E' un riferimento sperimentale, non un deployment reale.</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>rilevato; l'esecuzione/scelta e' di una fase successiva</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py (blocco [PARTIZIONE IID], strategia registrata in config.partition_strategy); config/experiment_rq2_iid.yaml; config/experiment_rq2_per_site.yaml</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga '[PARTIZIONE IID] ... conservando le numerosita' per client'; campo config.partition_strategy nei JSON prodotti da oggi</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Fase A — rilevato; l'esecuzione del confronto e' Fase E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="200" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Modello</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Architettura, parametri, normalizzazione, preprocessing; distinguere ordinario e modificato per i canary.</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Autoencoder denso. Regime naturale ORDINARIO: input_dim=6, lr=0.001, Adam, nessun dropout. Regime canary MODIFICATO: input_dim=7 con start_time_epoch, hidden_dims=(32,16), latent_dim=8, 1000 epoche locali. I due regimi non sono confrontabili fra loro.</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato. La distinzione ordinario/modificato richiesta dalla guida e' registrata e compare nel registro run nella colonna 'regime naturale o canary'.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>rilevato dalle evidenze</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>scripts/run_experiments.py::group_indices_by_site, entity_aware_split (riga 544), blocco cluster_shadow_universe in run_lira</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log riga 'Split (random) — train: N, hold-out: M'; risultati/matrice_confronti.xlsx riga C-RQ2</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>src/core/autoencoder.py; src/ml/autoencoder_trainer.py (Adam, riga 159); config/experiment.yaml; config/experiment_canary_balanced.yaml</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga 'AutoencoderTrainer [...] input_dim=..., hidden_dims=...'</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Fase A — rilevato dalle evidenze</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="185" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Modello</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Architettura, parametri, normalizzazione, preprocessing; distinguere ordinario e modificato per i canary.</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Autoencoder denso. Regime naturale ORDINARIO: input_dim=6, lr=0.001, ottimizzatore Adam, nessun dropout. Regime canary MODIFICATO: input_dim=7 con start_time_epoch, hidden_dims=(32,16), latent_dim=8, 1000 epoche locali. I due regimi non sono confrontabili fra loro.</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato. La distinzione ordinario/modificato richiesta dalla guida e' registrata ed e' riportata nel registro run nella colonna 'regime naturale o canary'.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
+    <row r="6" ht="200" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Algoritmo, μ, round, epoche locali, batch, ottimizzatore, scheduling e partecipazione dei client.</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>FedProx con proximal_mu = 0.01. 10 round FL, 50 epoche locali per round, batch_size 32, Adam lr 0.001. Tutti e 3 i client a ogni round, nessun campionamento. FedAvg pesato sul numero di campioni.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato. proximal_mu = 0.01 su 235 run su 235: nessun valore alternativo nelle evidenze. Il campo vive in cfg['ml'], non in cfg['experiment']: impostarlo nel posto sbagliato verrebbe ignorato in silenzio.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>rilevato dalle evidenze</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>src/core/autoencoder.py; src/ml/autoencoder_trainer.py (Adam, riga 159); config/experiment.yaml; config/experiment_canary_balanced.yaml</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log riga 'AutoencoderTrainer [...] device=cpu, input_dim=..., hidden_dims=...'</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>config/experiment.yaml (ml.proximal_mu); src/ml/fedavg_aggregator.py; scripts/build_run_registry.py</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log righe 'Round N — loss globale'; colonna 'algoritmo/mu' nel registro run; experiments/_registro_run.csv</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Fase A — rilevato dalle evidenze</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="185" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Algoritmo, μ, round, epoche locali, batch, ottimizzatore, scheduling e partecipazione dei client.</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>FedProx con proximal_mu = 0.01. 10 round FL nella campagna, 50 epoche locali per round, batch_size 32, Adam lr 0.001. Partecipazione: tutti e 3 i client a ogni round, nessun campionamento. Aggregazione FedAvg pesata sul numero di campioni.</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato. proximal_mu = 0.01 su 235 run su 235: nessun valore alternativo compare nelle evidenze. Il campo vive in cfg['ml'], non in cfg['experiment'].</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
+    <row r="7" ht="200" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Avversario</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Che cosa osserva, quando lo osserva e quali dati ausiliari possiede. Scegliere una superficie primaria per il primo confronto.</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Scenario 1: aggregatore honest-but-curious. Tre punti di osservazione ordinati sulla stessa pipeline, tutti e tre eseguiti: A1 update grezzo (dp-fedavg), A2 update clippato (central), A3 update clippato e rumorizzato (local). Dati ausiliari di fatto concessi alla calibrazione shadow: sessioni reali del client.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato per intero. I tre punti sono ORDINATI per informazione: A2 e A3 si ottengono da A1 applicando trasformazioni che distruggono informazione (clipping, poi rumore). Chi osserva A1 puo' calcolarsi A2 e A3 da solo; il contrario e' impossibile. Quindi A1 e' un limite superiore: se non c'e' segnale li', un nullo a A2 o A3 non puo' essere attribuito al rumore che sopprime un segnale altrimenti presente, perche' non ce n'era da sopprimere. La scelta della superficie primaria e' una decisione di disegno, non una proprieta' delle run.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>rilevato; l'esecuzione/scelta e' di una fase successiva</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py (--dp-mode, blocco privatize); src/ml/gradient_manager.py (clip_only, privatize); docs/paper/latex_dsn2027/sections/threat_model.tex</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga '[NO-DP BASELINE]' oppure 'GradientManager — eps=..., sigma=...'; colonna 'superficie dell'attacco' nel registro run</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Fase A — rilevato; la scelta della superficie primaria e' Fase B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="200" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Punto del rumore, clipping, unità/adiacenza, campionamento, σ, δ, accountant, composizione ed ε effettivo.</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Meccanismo gaussiano. Clipping L2 con C = max_grad_norm = 1.0. sigma = C*sqrt(2*ln(1.25/delta))/epsilon; con delta=1e-5 ed epsilon=1.0 si ottiene sigma=4.8448. Adiacenza CLIENT-level: clipping e rumore una volta per round sull'update del client, 50 epoche locali dentro il round, nessun clipping per-campione, quindi NON e' DP-SGD. Nessun campionamento, nessuna amplificazione. Epsilon nelle evidenze: 1.0, 0.5, 0.1, piu' 8.0 e 16.0 a un solo seed. Composizione base e avanzata entrambe riportate; nessun accountant RDP; nessun enforcement.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato. Limite dichiarato: non essendo DP-SGD, l'epsilon per round e' un'etichetta di configurazione che calibra il rumore, non una garanzia per round verificata. Comporre un'etichetta produce un'etichetta.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>rilevato dalle evidenze</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>config/experiment.yaml (ml.proximal_mu, ml.epochs, ml.batch_size); src/ml/fedavg_aggregator.py; scripts/build_run_registry.py per il conteggio</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log righe 'Round N — loss globale'; risultati/matrice_run_completati.xlsx colonna 'algoritmo/μ'; experiments/_registro_run.csv</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>src/ml/gradient_manager.py::_compute_sigma (riga 200), privatize, clip_only; src/ml/privacy_auditor.py</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga 'GradientManager — eps=1.0, delta=1e-05, max_norm=1.0, sigma=4.8448'; campi config.epsilon_cumulative_* nei JSON</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Fase A — rilevato dalle evidenze</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="185" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Avversario</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Che cosa osserva, quando lo osserva e quali dati ausiliari possiede. Scegliere una superficie primaria per il primo confronto.</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Scenario 1: aggregatore honest-but-curious. Tre punti di osservazione sulla stessa pipeline, tutti e tre eseguiti: A1 update grezzo (dp-fedavg), A2 update clippato (central), A3 update clippato e rumorizzato (local). Dati ausiliari di fatto concessi alla calibrazione shadow: sessioni reali del client.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato per intero. La scelta della superficie PRIMARIA non compare in queste evidenze perche' non e' una proprieta' delle run: e' una decisione di disegno della campagna centrale.</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>rilevato; una parte e' decisione di Fase B</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>scripts/run_experiments.py (--dp-mode e blocco privatize); src/ml/gradient_manager.py; docs/paper/latex_dsn2027/sections/threat_model.tex</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log riga '[NO-DP BASELINE]' oppure 'GradientManager — ε=..., σ=...'; colonna 'superficie dell'attacco' nel registro run</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Fase A — rilevato; la scelta della superficie primaria e' Fase B</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="185" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Punto del rumore, clipping, unità/adiacenza, campionamento, σ, δ, accountant, composizione ed ε effettivo.</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Meccanismo gaussiano. Clipping L2 con C = max_grad_norm = 1.0. sigma = C * sqrt(2*ln(1.25/delta)) / epsilon; con delta = 1e-5 ed epsilon = 1.0 si ottiene sigma = 4.8448. Adiacenza CLIENT-level: clipping e rumore una volta per round sull'update del client, 50 epoche locali dentro il round, nessun clipping per-campione, quindi non e' DP-SGD. Nessun campionamento, quindi nessuna amplificazione. Epsilon presenti nelle evidenze: 1.0, 0.5, 0.1, piu' 8.0 e 16.0 a un solo seed. Accounting: composizione base ed avanzata entrambe riportate, nessun accountant RDP, nessun enforcement del budget.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato. Registrato anche il limite dichiarato: non essendo DP-SGD, l'epsilon per round e' un'etichetta di configurazione che calibra il rumore, non una garanzia per round verificata.</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
+    <row r="9" ht="200" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Misura</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Attacchi/versioni, calibrazione, soglie, metriche primarie e secondarie, incertezza e unità di replica.</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Tre attacchi: Yeom 2018 (modello globale), Shadow MIA (calibrato), LiRA (update per-client), piu' il LiRA composto sui round. n_shadow = 16 nella campagna. Metrica primaria usata finora: AUC-ROC. Secondarie nei JSON: TPR@1%FPR, MIA Advantage, matrice di confusione alla soglia ottimale. Bootstrap a 10.000 ricampionamenti. Unita' di replica: il seed, 5 per cella.</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato, con tre proprieta' MISURATE della misura stessa: (1) sigma di LiRA colpisce il floor nel 97-99% dei record, e l'ablation a 32 shadow ha falsificato l'ipotesi che dipendesse dal numero di shadow — la causa e' che il floor deriva dalla varianza FRA RECORD ed e' ~10x piu' largo dell'intero intervallo delle loss; (2) LiRA non e' riproducibile a seed fisso, la loss grezza si'; (3) check_significance.py deduplica per (dp_mode, epsilon, seed) scegliendo il file piu' recente.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>rilevato dalle evidenze</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>src/ml/gradient_manager.py::_compute_sigma (riga 200), privatize, clip_only; src/ml/privacy_auditor.py</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log riga 'GradientManager — ε=1.0, δ=1e-05, max_norm=1.0, σ=4.8448'; campi config.epsilon_cumulative_* nei JSON</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py::run_yeom, run_shadow, run_lira; scripts/check_significance.py; scripts/genera_matrici_faseA.py</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga 'LiRA diagnostica: ... floor_hit=...'; logs/abl_nshadow32_s42.log e logs/abl_indepfloor_s42.log</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Fase A — rilevato dalle evidenze</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="185" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Misura</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Attacchi/versioni, calibrazione, soglie, metriche primarie e secondarie, incertezza e unità di replica.</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Tre attacchi: Yeom 2018 (loss-based sul modello globale), Shadow MIA (calibrato), LiRA (Carlini 2022, sugli update per-client), piu' il punteggio LiRA composto sui round. n_shadow = 16 nella campagna. Metrica primaria usata finora: AUC-ROC. Secondarie presenti nei JSON: TPR@1%FPR, MIA Advantage, matrice di confusione alla soglia ottimale. Incertezza: bootstrap a 10.000 ricampionamenti. Unita' di replica: il seed, 5 per cella.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato, con tre proprieta' misurate della misura stessa: (1) sigma di LiRA colpisce il floor nel 97-99% dei record, e l'ablation a 32 shadow mostra che non dipende dal numero di shadow; (2) LiRA non e' riproducibile a seed fisso, la loss grezza si'; (3) check_significance.py deduplica per (dp_mode, epsilon, seed) scegliendo il file piu' recente.</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
+    <row r="10" ht="200" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Costo</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Errore di ricostruzione su holdout naturale, per sito e aggregato; risorse se misurate.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Errore di ricostruzione (MSE) sull'holdout naturale. AGGREGATO: campo per_round[*].fl.mean_loss nei JSON. PER SITO: tabulato il 2026-09-21 nel foglio 'Costo_per_sito' di Matrice_sintesi.xlsx, 133 righe (log x sito) con la loss dell'ultimo round e la numerosita' del client. Nessuna misura sistematica di risorse, a parte l'overhead del Privacy Auditor.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CORREZIONE di quanto scritto nella versione precedente di questa scheda: avevo affermato che il dato per client fosse 'nella stessa struttura' dei JSON. NON e' vero. per_round[*].fl contiene solo mean_loss globale e nessuna chiave nomina un client o un sito: verificato scorrendo ricorsivamente le chiavi. La loss per client esiste SOLO nella riga di log '[&lt;sito&gt;-NN] Round R — loss=..., n=...'. La tabella e' stata costruita da li'.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>rilevato dalle evidenze</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>scripts/run_experiments.py::run_yeom, run_shadow, run_lira; scripts/check_significance.py; scripts/genera_matrici_faseA.py</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log righe 'LiRA diagnostica: ... floor_hit=...'; logs/abl_nshadow32_s42.log e logs/abl_indepfloor_s42.log per l'ablation</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Fase A — rilevato dalle evidenze</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="185" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Costo</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Errore di ricostruzione su holdout naturale, per sito e aggregato; risorse se misurate.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Errore di ricostruzione (MSE) sull'holdout naturale, presente nei JSON come mean_loss globale per ogni round. Il dato per client esiste nella stessa struttura. Nessuna misura sistematica di risorse, a parte l'overhead del Privacy Auditor.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato come disponibile. Non e' mai stato tabulato per sito: e' un'estrazione dai JSON gia' presenti, non un dato mancante.</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>rilevato dalle evidenze</t>
-        </is>
-      </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>scripts/run_experiments.py::run_fl_rounds (campo fl.mean_loss per round); scripts/generate_excel_report.py</t>
+          <t>scripts/genera_matrici_faseA.py::scrivi_costo_per_sito; scripts/run_experiments.py::run_fl_rounds</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>logs/*.log riga 'Round N — loss globale: ...'; campo per_round[*].fl.mean_loss nei JSON di experiments/</t>
+          <t>logs/*.log riga '[office1-01] Round N — loss=..., n=...'; foglio 'Costo_per_sito' in risultati/Matrice_sintesi.xlsx</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -951,39 +951,31 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Verde: lo stato e' interamente ricavabile dalle evidenze su disco. Resta da CONFERMARE come decisione deliberata prima di aprire la Fase B.</t>
+          <t>Verde: lo stato e' interamente ricavabile dalle evidenze. Resta da CONFERMARE come decisione deliberata prima di aprire la Fase B.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Giallo: lo stato e' rilevato, ma una parte del campo richiede una decisione di disegno che appartiene alla Fase B e non a questa scheda.</t>
+          <t>Giallo: lo stato e' rilevato, ma l'esecuzione o la scelta appartengono a una fase successiva.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>RIMOSSO da questa scheda, perche' non e' Fase A: ogni raccomandazione, proposta di rerun e lacuna sperimentale. Quelle stanno in risultati/Matrice_sintesi.xlsx, colonne 'lacuna effettiva' e 'minimo rerun necessario'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>La colonna 'Decisione scelta' descrive cosa fanno OGGI codice e dati. Non e' ancora una decisione congelata.</t>
+          <t>Non e' in questa scheda, perche' non e' Fase A: raccomandazioni, proposte di rerun e lacune sperimentali. Stanno in risultati/Matrice_sintesi.xlsx.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E10"/>
-  <mergeCells count="5">
-    <mergeCell ref="A15:H15"/>
+  <mergeCells count="4">
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A15:H15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -999,10 +991,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
@@ -1050,7 +1042,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="185" customHeight="1">
+    <row r="2" ht="200" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Popolazione e dati</t>
@@ -1063,12 +1055,12 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>ACN-Data, 3 siti reali: caltech, jpl, office1. Anni 2018-2021, office1 dal 2019 (il 2018 non esiste su ev.caltech.edu). Sessioni caricate: caltech 31.404, jpl 33.629, office1 1.680. Nessun filtro oltre allo scarto delle sessioni prive delle feature richieste. 6 feature nel regime naturale: total_energy_kwh, max_power_kw, kwh_requested, minutes_available, hour_of_day, duration_hours. Normalizzazione min-max [0,1] calcolata sul training. hour_of_day localizzato al fuso del sito.</t>
+          <t>ACN-Data, 3 siti reali: caltech, jpl, office1. Anni 2018-2021, office1 dal 2019. Sessioni: caltech 31.404, jpl 33.629, office1 1.680 (66.713 totali). Nessun filtro oltre allo scarto delle sessioni prive delle feature richieste. 6 feature nel regime naturale; normalizzazione min-max [0,1] sul training; hour_of_day localizzato al fuso del sito. IDENTIFICATIVI, misurati il 2026-09-21: sessionID 100%, stationID 100%, spaceID 100%, userID 72,6% globale ma molto diseguale fra siti — jpl 93,5%, caltech 52,1%, office1 34,8%.</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Rilevato, non ancora congelato. Identificativi disponibili nel dataset: session_id e user_id; il grado di popolamento di user_id NON e' stato misurato, quindi l'unita' 'persona' non e' ne' esclusa ne' sostenuta dalle evidenze attuali.</t>
+          <t>Rilevato e misurato. Su userID: e' l'unico identificativo che potrebbe sostenere un'unita' 'persona', ed e' anche l'unico non completo. Con office1 al 34,8% un'analisi per persona su quel sito lavorerebbe su un terzo dei dati, con selezione non casuale (chi si registra al servizio). sessionID, stationID e spaceID sono completi ma identificano la sessione o il punto di ricarica, non l'individuo.</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -1078,12 +1070,12 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>src/adapters/acn_dataset.py; scripts/run_experiments.py::enrich_sessions, normalize_sessions; config/experiment.yaml (sites:, ml.input_dim, ml.feature_names)</t>
+          <t>scripts/genera_matrici_faseA.py (misura del popolamento); src/adapters/acn_dataset.py; scripts/run_experiments.py::enrich_sessions, normalize_sessions</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>logs/*.log riga 'sessioni caricate' per ogni run; campo config.n_train_sessions nei JSON di experiments/</t>
+          <t>logs/*.log riga 'sessioni caricate'; campo config.n_train_sessions nei JSON; datasets/acn/*/acndata_sessions_*.json per il conteggio degli identificativi</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
@@ -1092,7 +1084,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="185" customHeight="1">
+    <row r="3" ht="200" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Unità di membership</t>
@@ -1110,7 +1102,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Rilevato e coerente. Il meccanismo DP opera su adiacenza CLIENT-level mentre gli attacchi misurano il RECORD: le due unita' non coincidono. E' un fatto registrato, non un difetto da correggere.</t>
+          <t>Rilevato e coerente. Il meccanismo DP opera su adiacenza CLIENT-level mentre gli attacchi misurano il RECORD: le due unita' non coincidono. E' un fatto registrato, non un difetto da correggere. L'unita' 'persona' resta impraticabile su office1 per il popolamento di userID (vedi riga Popolazione).</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -1120,7 +1112,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>scripts/run_experiments.py::run_yeom, run_shadow, run_lira (il pool di valutazione e' una lista di sessioni)</t>
+          <t>scripts/run_experiments.py::run_yeom, run_shadow, run_lira</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -1134,7 +1126,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="185" customHeight="1">
+    <row r="4" ht="200" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Partizioni</t>
@@ -1147,279 +1139,279 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Split train/holdout 80/20 casuale, previo shuffle con il seed dell'esperimento. cfg['split']['strategy'] esiste con default 'random'; l'alternativa 'entity_aware' non e' impostata in nessun config di campagna. Assegnazione ai client per site_id reale: 3 client = 3 siti. Dati ausiliari dell'attacco: gli shadow di LiRA si addestrano su cluster_members[c] + cluster_holdout[c], cioe' sessioni reali del client; IN/OUT per shadow su meta' dell'universo.</t>
+          <t>Split train/holdout 80/20 casuale previo shuffle con il seed. ASSEGNAZIONE AI CLIENT, dal 2026-09-21 esplicita e registrata: partition.strategy con due valori. 'per_site' (default, storico) = i 3 client SONO i 3 siti, non-IID per natura. 'iid' (nuovo) = sessioni rimescolate FRA i siti conservando esattamente le numerosita' per client, quindi cambia solo la distribuzione delle feature. Dati ausiliari dell'attacco: shadow LiRA su cluster_members[c] + cluster_holdout[c].</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Rilevato. Conseguenza registrata, non risolta: la partizione e' non-IID perche' i client SONO i siti, quindi l'eterogeneita' non e' un fattore manipolato. Nessun riferimento omogeneo esiste fra le 235 run.</t>
+          <t>Rilevato E COLMATO come capacita': il braccio IID ora esiste nel codice e nei config (experiment_rq2_iid.yaml contro experiment_rq2_per_site.yaml, identici tranne quel campo). Non e' ancora stato ESEGUITO: la lacuna sperimentale di RQ2 resta aperta e vive in Matrice_sintesi. Da dichiarare nel paper: la partizione IID rompe la corrispondenza client-sito e con essa la coerenza temporale e la separazione fra utenti. E' un riferimento sperimentale, non un deployment reale.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py (blocco [PARTIZIONE IID], strategia registrata in config.partition_strategy); config/experiment_rq2_iid.yaml; config/experiment_rq2_per_site.yaml</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga '[PARTIZIONE IID] ... conservando le numerosita' per client'; campo config.partition_strategy nei JSON prodotti da oggi</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Fase A — rilevato; l'esecuzione del confronto e' Fase E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="200" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Modello</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Architettura, parametri, normalizzazione, preprocessing; distinguere ordinario e modificato per i canary.</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Autoencoder denso. Regime naturale ORDINARIO: input_dim=6, lr=0.001, Adam, nessun dropout. Regime canary MODIFICATO: input_dim=7 con start_time_epoch, hidden_dims=(32,16), latent_dim=8, 1000 epoche locali. I due regimi non sono confrontabili fra loro.</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato. La distinzione ordinario/modificato richiesta dalla guida e' registrata e compare nel registro run nella colonna 'regime naturale o canary'.</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>scripts/run_experiments.py::group_indices_by_site, entity_aware_split (riga 544), blocco cluster_shadow_universe in run_lira</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log riga 'Split (random) — train: N, hold-out: M'; risultati/matrice_confronti.xlsx riga C-RQ2</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>src/core/autoencoder.py; src/ml/autoencoder_trainer.py (Adam, riga 159); config/experiment.yaml; config/experiment_canary_balanced.yaml</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga 'AutoencoderTrainer [...] input_dim=..., hidden_dims=...'</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Fase A — rilevato dalle evidenze</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="185" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Modello</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Architettura, parametri, normalizzazione, preprocessing; distinguere ordinario e modificato per i canary.</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Autoencoder denso. Regime naturale ORDINARIO: input_dim=6, lr=0.001, ottimizzatore Adam, nessun dropout. Regime canary MODIFICATO: input_dim=7 con start_time_epoch, hidden_dims=(32,16), latent_dim=8, 1000 epoche locali. I due regimi non sono confrontabili fra loro.</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato. La distinzione ordinario/modificato richiesta dalla guida e' registrata ed e' riportata nel registro run nella colonna 'regime naturale o canary'.</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+    <row r="6" ht="200" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Algoritmo, μ, round, epoche locali, batch, ottimizzatore, scheduling e partecipazione dei client.</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>FedProx con proximal_mu = 0.01. 10 round FL, 50 epoche locali per round, batch_size 32, Adam lr 0.001. Tutti e 3 i client a ogni round, nessun campionamento. FedAvg pesato sul numero di campioni.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato. proximal_mu = 0.01 su 235 run su 235: nessun valore alternativo nelle evidenze. Il campo vive in cfg['ml'], non in cfg['experiment']: impostarlo nel posto sbagliato verrebbe ignorato in silenzio.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>src/core/autoencoder.py; src/ml/autoencoder_trainer.py (Adam, riga 159); config/experiment.yaml; config/experiment_canary_balanced.yaml</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log riga 'AutoencoderTrainer [...] device=cpu, input_dim=..., hidden_dims=...'</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>config/experiment.yaml (ml.proximal_mu); src/ml/fedavg_aggregator.py; scripts/build_run_registry.py</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log righe 'Round N — loss globale'; colonna 'algoritmo/mu' nel registro run; experiments/_registro_run.csv</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Fase A — rilevato dalle evidenze</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="185" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Algoritmo, μ, round, epoche locali, batch, ottimizzatore, scheduling e partecipazione dei client.</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>FedProx con proximal_mu = 0.01. 10 round FL nella campagna, 50 epoche locali per round, batch_size 32, Adam lr 0.001. Partecipazione: tutti e 3 i client a ogni round, nessun campionamento. Aggregazione FedAvg pesata sul numero di campioni.</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato. proximal_mu = 0.01 su 235 run su 235: nessun valore alternativo compare nelle evidenze. Il campo vive in cfg['ml'], non in cfg['experiment'].</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+    <row r="7" ht="200" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Avversario</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Che cosa osserva, quando lo osserva e quali dati ausiliari possiede. Scegliere una superficie primaria per il primo confronto.</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Scenario 1: aggregatore honest-but-curious. Tre punti di osservazione ordinati sulla stessa pipeline, tutti e tre eseguiti: A1 update grezzo (dp-fedavg), A2 update clippato (central), A3 update clippato e rumorizzato (local). Dati ausiliari di fatto concessi alla calibrazione shadow: sessioni reali del client.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato per intero. I tre punti sono ORDINATI per informazione: A2 e A3 si ottengono da A1 applicando trasformazioni che distruggono informazione (clipping, poi rumore). Chi osserva A1 puo' calcolarsi A2 e A3 da solo; il contrario e' impossibile. Quindi A1 e' un limite superiore: se non c'e' segnale li', un nullo a A2 o A3 non puo' essere attribuito al rumore che sopprime un segnale altrimenti presente, perche' non ce n'era da sopprimere. La scelta della superficie primaria e' una decisione di disegno, non una proprieta' delle run.</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py (--dp-mode, blocco privatize); src/ml/gradient_manager.py (clip_only, privatize); docs/paper/latex_dsn2027/sections/threat_model.tex</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga '[NO-DP BASELINE]' oppure 'GradientManager — eps=..., sigma=...'; colonna 'superficie dell'attacco' nel registro run</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Fase A — rilevato; la scelta della superficie primaria e' Fase B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="200" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Punto del rumore, clipping, unità/adiacenza, campionamento, σ, δ, accountant, composizione ed ε effettivo.</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Meccanismo gaussiano. Clipping L2 con C = max_grad_norm = 1.0. sigma = C*sqrt(2*ln(1.25/delta))/epsilon; con delta=1e-5 ed epsilon=1.0 si ottiene sigma=4.8448. Adiacenza CLIENT-level: clipping e rumore una volta per round sull'update del client, 50 epoche locali dentro il round, nessun clipping per-campione, quindi NON e' DP-SGD. Nessun campionamento, nessuna amplificazione. Epsilon nelle evidenze: 1.0, 0.5, 0.1, piu' 8.0 e 16.0 a un solo seed. Composizione base e avanzata entrambe riportate; nessun accountant RDP; nessun enforcement.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato. Limite dichiarato: non essendo DP-SGD, l'epsilon per round e' un'etichetta di configurazione che calibra il rumore, non una garanzia per round verificata. Comporre un'etichetta produce un'etichetta.</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>config/experiment.yaml (ml.proximal_mu, ml.epochs, ml.batch_size); src/ml/fedavg_aggregator.py; scripts/build_run_registry.py per il conteggio</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log righe 'Round N — loss globale'; risultati/matrice_run_completati.xlsx colonna 'algoritmo/μ'; experiments/_registro_run.csv</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>src/ml/gradient_manager.py::_compute_sigma (riga 200), privatize, clip_only; src/ml/privacy_auditor.py</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga 'GradientManager — eps=1.0, delta=1e-05, max_norm=1.0, sigma=4.8448'; campi config.epsilon_cumulative_* nei JSON</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Fase A — rilevato dalle evidenze</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="185" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Avversario</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Che cosa osserva, quando lo osserva e quali dati ausiliari possiede. Scegliere una superficie primaria per il primo confronto.</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Scenario 1: aggregatore honest-but-curious. Tre punti di osservazione sulla stessa pipeline, tutti e tre eseguiti: A1 update grezzo (dp-fedavg), A2 update clippato (central), A3 update clippato e rumorizzato (local). Dati ausiliari di fatto concessi alla calibrazione shadow: sessioni reali del client.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato per intero. La scelta della superficie PRIMARIA non compare in queste evidenze perche' non e' una proprieta' delle run: e' una decisione di disegno della campagna centrale.</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>scripts/run_experiments.py (--dp-mode e blocco privatize); src/ml/gradient_manager.py; docs/paper/latex_dsn2027/sections/threat_model.tex</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log riga '[NO-DP BASELINE]' oppure 'GradientManager — ε=..., σ=...'; colonna 'superficie dell'attacco' nel registro run</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Fase A — rilevato; la scelta della superficie primaria e' Fase B</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="185" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Punto del rumore, clipping, unità/adiacenza, campionamento, σ, δ, accountant, composizione ed ε effettivo.</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Meccanismo gaussiano. Clipping L2 con C = max_grad_norm = 1.0. sigma = C * sqrt(2*ln(1.25/delta)) / epsilon; con delta = 1e-5 ed epsilon = 1.0 si ottiene sigma = 4.8448. Adiacenza CLIENT-level: clipping e rumore una volta per round sull'update del client, 50 epoche locali dentro il round, nessun clipping per-campione, quindi non e' DP-SGD. Nessun campionamento, quindi nessuna amplificazione. Epsilon presenti nelle evidenze: 1.0, 0.5, 0.1, piu' 8.0 e 16.0 a un solo seed. Accounting: composizione base ed avanzata entrambe riportate, nessun accountant RDP, nessun enforcement del budget.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato. Registrato anche il limite dichiarato: non essendo DP-SGD, l'epsilon per round e' un'etichetta di configurazione che calibra il rumore, non una garanzia per round verificata.</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+    <row r="9" ht="200" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Misura</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Attacchi/versioni, calibrazione, soglie, metriche primarie e secondarie, incertezza e unità di replica.</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Tre attacchi: Yeom 2018 (modello globale), Shadow MIA (calibrato), LiRA (update per-client), piu' il LiRA composto sui round. n_shadow = 16 nella campagna. Metrica primaria usata finora: AUC-ROC. Secondarie nei JSON: TPR@1%FPR, MIA Advantage, matrice di confusione alla soglia ottimale. Bootstrap a 10.000 ricampionamenti. Unita' di replica: il seed, 5 per cella.</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Rilevato, con tre proprieta' MISURATE della misura stessa: (1) sigma di LiRA colpisce il floor nel 97-99% dei record, e l'ablation a 32 shadow ha falsificato l'ipotesi che dipendesse dal numero di shadow — la causa e' che il floor deriva dalla varianza FRA RECORD ed e' ~10x piu' largo dell'intero intervallo delle loss; (2) LiRA non e' riproducibile a seed fisso, la loss grezza si'; (3) check_significance.py deduplica per (dp_mode, epsilon, seed) scegliendo il file piu' recente.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>src/ml/gradient_manager.py::_compute_sigma (riga 200), privatize, clip_only; src/ml/privacy_auditor.py</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log riga 'GradientManager — ε=1.0, δ=1e-05, max_norm=1.0, σ=4.8448'; campi config.epsilon_cumulative_* nei JSON</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py::run_yeom, run_shadow, run_lira; scripts/check_significance.py; scripts/genera_matrici_faseA.py</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>logs/*.log riga 'LiRA diagnostica: ... floor_hit=...'; logs/abl_nshadow32_s42.log e logs/abl_indepfloor_s42.log</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Fase A — rilevato dalle evidenze</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="185" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Misura</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Attacchi/versioni, calibrazione, soglie, metriche primarie e secondarie, incertezza e unità di replica.</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Tre attacchi: Yeom 2018 (loss-based sul modello globale), Shadow MIA (calibrato), LiRA (Carlini 2022, sugli update per-client), piu' il punteggio LiRA composto sui round. n_shadow = 16 nella campagna. Metrica primaria usata finora: AUC-ROC. Secondarie presenti nei JSON: TPR@1%FPR, MIA Advantage, matrice di confusione alla soglia ottimale. Incertezza: bootstrap a 10.000 ricampionamenti. Unita' di replica: il seed, 5 per cella.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato, con tre proprieta' misurate della misura stessa: (1) sigma di LiRA colpisce il floor nel 97-99% dei record, e l'ablation a 32 shadow mostra che non dipende dal numero di shadow; (2) LiRA non e' riproducibile a seed fisso, la loss grezza si'; (3) check_significance.py deduplica per (dp_mode, epsilon, seed) scegliendo il file piu' recente.</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+    <row r="10" ht="200" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Costo</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Errore di ricostruzione su holdout naturale, per sito e aggregato; risorse se misurate.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Errore di ricostruzione (MSE) sull'holdout naturale. AGGREGATO: campo per_round[*].fl.mean_loss nei JSON. PER SITO: tabulato il 2026-09-21 nel foglio 'Costo_per_sito' di Matrice_sintesi.xlsx, 133 righe (log x sito) con la loss dell'ultimo round e la numerosita' del client. Nessuna misura sistematica di risorse, a parte l'overhead del Privacy Auditor.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CORREZIONE di quanto scritto nella versione precedente di questa scheda: avevo affermato che il dato per client fosse 'nella stessa struttura' dei JSON. NON e' vero. per_round[*].fl contiene solo mean_loss globale e nessuna chiave nomina un client o un sito: verificato scorrendo ricorsivamente le chiavi. La loss per client esiste SOLO nella riga di log '[&lt;sito&gt;-NN] Round R — loss=..., n=...'. La tabella e' stata costruita da li'.</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>☑</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>scripts/run_experiments.py::run_yeom, run_shadow, run_lira; scripts/check_significance.py; scripts/genera_matrici_faseA.py</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>logs/*.log righe 'LiRA diagnostica: ... floor_hit=...'; logs/abl_nshadow32_s42.log e logs/abl_indepfloor_s42.log per l'ablation</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Fase A — rilevato dalle evidenze</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="185" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Costo</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Errore di ricostruzione su holdout naturale, per sito e aggregato; risorse se misurate.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Errore di ricostruzione (MSE) sull'holdout naturale, presente nei JSON come mean_loss globale per ogni round. Il dato per client esiste nella stessa struttura. Nessuna misura sistematica di risorse, a parte l'overhead del Privacy Auditor.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Rilevato come disponibile. Non e' mai stato tabulato per sito: e' un'estrazione dai JSON gia' presenti, non un dato mancante.</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>☑</t>
-        </is>
-      </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>scripts/run_experiments.py::run_fl_rounds (campo fl.mean_loss per round); scripts/generate_excel_report.py</t>
+          <t>scripts/genera_matrici_faseA.py::scrivi_costo_per_sito; scripts/run_experiments.py::run_fl_rounds</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>logs/*.log riga 'Round N — loss globale: ...'; campo per_round[*].fl.mean_loss nei JSON di experiments/</t>
+          <t>logs/*.log riga '[office1-01] Round N — loss=..., n=...'; foglio 'Costo_per_sito' in risultati/Matrice_sintesi.xlsx</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">

--- a/risultati/decision_matrix_ACN_membership_DP.xlsx
+++ b/risultati/decision_matrix_ACN_membership_DP.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -141,6 +141,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -508,8 +512,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -941,29 +945,288 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>DECISIONI CONGELATE PRIMA DI E-A — ESPERIMENTI.md §0 (confermate dall'utente il 2026-09-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Metrica primaria di attacco</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Da congelare prima di leggere i risultati di E-A (guida, sezioni 5 e 8; ESPERIMENTI.md §0).</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Loss grezza (Yeom) sul modello globale e conteggio per record con z sui composed_score di LiRA; LiRA calibrato e Shadow come secondarie.</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente (Assunta Imperatrice) il 2026-09-22 prima del lancio di E-A, secondo il protocollo di CLAUDE.md §3. Motivazione: LiRA calibrato è degenere (STATO.md §3.4, segnalazioni 10-13); la loss grezza è riproducibile a seed fisso, LiRA no.</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>confermata (congelata) — 2026-09-22</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py::run_yeom; scripts/worst_case_livello_di_caso.py (z per record, dopo segnalazione 6)</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0; docs/STATO.md §3.4</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Superficie primaria</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Scegliere una superficie primaria per il primo confronto (guida, sezione 5, campo Avversario).</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Update del singolo client (A1-A3) per il per-record; modello globale per Yeom e Shadow, come nella campagna.</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Coerente con la riga 'Avversario' di questa stessa scheda (D7): A1 è un limite superiore su A2/A3.</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>confermata (congelata) — 2026-09-22</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py (--dp-mode, blocco privatize); src/ml/gradient_manager.py</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>FPR operativo</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Fissare un FPR operativo sostenibile dai dati (guida, sezione 8).</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>1%, con TPR = FPR come livello di caso; 0.1% solo dove la numerosità lo sostiene.</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Con 20 template OUT un falso positivo vale il 5%: non è base sufficiente per FPR 0.1% (guida §8).</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>confermata (congelata) — 2026-09-22</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py (TPR@FPR); scripts/check_significance.py</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0; guida §8</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Costo accettabile</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Fissare una soglia di costo accettabile per la loss di ricostruzione (guida, sezione 8; STATO.md §3.8).</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Loss finale entro 3 volte il riferimento no-DP (pilot: ε=16 sta a 2.6x, ε=8 a 4.6x).</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Le celle a ε in {1, 0.5, 0.1} restano oltre 100x il riferimento e sono fuori soglia (STATO.md §3.1).</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>confermata (congelata) — 2026-09-22</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>scripts/genera_matrici_faseA.py; risultati/Matrice_sintesi.xlsx foglio Utility_privacy_limite</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0; docs/STATO.md §3.1, §3.8</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Margine di equivalenza</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Fissare un margine di equivalenza per il test TOST su AUC (guida, sezione 8).</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>AUC entro 0.02 da 0.5 (TOST), come già in check_significance.py.</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Il margine vale per AUC; non vale automaticamente per TPR (guida §8) e richiede motivazione separata se esteso.</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>confermata (congelata) — 2026-09-22</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>scripts/check_significance.py</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0; guida §8</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Unità di replica</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Definire l'unità di replica per calibrazione, repliche e potenza (guida, sezione 8).</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Il seed; 5 seed per cella. Le copie di un canary non sono repliche indipendenti.</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Seed fissi per E-A: 42, 123, 456, 789, 1234, uno per run nella stessa sweep-dir.</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>confermata (congelata) — 2026-09-22</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py --seed; ESPERIMENTI.md 'Regole che valgono per tutti'</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>LEGENDA — questa scheda e' la sezione 5 della guida, il cancello fra Fase A e Fase B.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Verde: lo stato e' interamente ricavabile dalle evidenze. Resta da CONFERMARE come decisione deliberata prima di aprire la Fase B.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Giallo: lo stato e' rilevato, ma l'esecuzione o la scelta appartengono a una fase successiva.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Non e' in questa scheda, perche' non e' Fase A: raccomandazioni, proposte di rerun e lacune sperimentali. Stanno in risultati/Matrice_sintesi.xlsx.</t>
         </is>
@@ -971,11 +1234,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E10"/>
-  <mergeCells count="4">
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A15:H15"/>
+  <mergeCells count="5">
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A11:H11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -987,8 +1251,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -1420,6 +1684,265 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>DECISIONI CONGELATE PRIMA DI E-A — ESPERIMENTI.md §0 (confermate dall'utente il 2026-09-22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Metrica primaria di attacco</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Da congelare prima di leggere i risultati di E-A (guida, sezioni 5 e 8; ESPERIMENTI.md §0).</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Loss grezza (Yeom) sul modello globale e conteggio per record con z sui composed_score di LiRA; LiRA calibrato e Shadow come secondarie.</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente (Assunta Imperatrice) il 2026-09-22 prima del lancio di E-A, secondo il protocollo di CLAUDE.md §3. Motivazione: LiRA calibrato è degenere (STATO.md §3.4, segnalazioni 10-13); la loss grezza è riproducibile a seed fisso, LiRA no.</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py::run_yeom; scripts/worst_case_livello_di_caso.py (z per record, dopo segnalazione 6)</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0; docs/STATO.md §3.4</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Superficie primaria</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Scegliere una superficie primaria per il primo confronto (guida, sezione 5, campo Avversario).</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Update del singolo client (A1-A3) per il per-record; modello globale per Yeom e Shadow, come nella campagna.</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Coerente con la riga 'Avversario' di questa stessa scheda (D7): A1 è un limite superiore su A2/A3.</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py (--dp-mode, blocco privatize); src/ml/gradient_manager.py</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>FPR operativo</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Fissare un FPR operativo sostenibile dai dati (guida, sezione 8).</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>1%, con TPR = FPR come livello di caso; 0.1% solo dove la numerosità lo sostiene.</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Con 20 template OUT un falso positivo vale il 5%: non è base sufficiente per FPR 0.1% (guida §8).</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py (TPR@FPR); scripts/check_significance.py</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0; guida §8</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Costo accettabile</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Fissare una soglia di costo accettabile per la loss di ricostruzione (guida, sezione 8; STATO.md §3.8).</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Loss finale entro 3 volte il riferimento no-DP (pilot: ε=16 sta a 2.6x, ε=8 a 4.6x).</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Le celle a ε in {1, 0.5, 0.1} restano oltre 100x il riferimento e sono fuori soglia (STATO.md §3.1).</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>scripts/genera_matrici_faseA.py; risultati/Matrice_sintesi.xlsx foglio Utility_privacy_limite</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0; docs/STATO.md §3.1, §3.8</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Margine di equivalenza</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Fissare un margine di equivalenza per il test TOST su AUC (guida, sezione 8).</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>AUC entro 0.02 da 0.5 (TOST), come già in check_significance.py.</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Il margine vale per AUC; non vale automaticamente per TPR (guida §8) e richiede motivazione separata se esteso.</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>scripts/check_significance.py</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0; guida §8</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Unità di replica</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Definire l'unità di replica per calibrazione, repliche e potenza (guida, sezione 8).</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Il seed; 5 seed per cella. Le copie di un canary non sono repliche indipendenti.</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Proposta di ESPERIMENTI.md §0, confermata dall'utente il 2026-09-22. Seed fissi per E-A: 42, 123, 456, 789, 1234, uno per run nella stessa sweep-dir.</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>scripts/run_experiments.py --seed; ESPERIMENTI.md 'Regole che valgono per tutti'</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>docs/ESPERIMENTI.md §0</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>Cancello Fase A → Fase B (guida §7)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
